--- a/ig/DM-OCTOBRE-2025/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
+++ b/ig/DM-OCTOBRE-2025/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="1433">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250918120000</t>
+    <t>20251017120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T12:00:00+01:00</t>
+    <t>2025-10-17T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -415,7 +415,7 @@
     <t>035</t>
   </si>
   <si>
-    <t>Coordination hospitalière de prélèvement d'organes</t>
+    <t>Coordination hospitalière de prélèvement d'organe</t>
   </si>
   <si>
     <t>Equipe pluriprofessionnelle de professionnels de santé, ayant pour mission d'organiser et de coordonner les dons d'organes et de tissus, d'assurer le lien entre les différents acteurs de la chaîne de don, de garantir le respect des procédures et des bonnes pratiques légales éthiques et techniques, d'organiser la prise en charge du donneur et d'accompagner les proches tout au long du processus de don.</t>
@@ -4288,25 +4288,31 @@
     <t>Prise en charge coordonnée des patients atteints de maladies rares</t>
   </si>
   <si>
+    <t>Organisation de soins qui dispense  pour les personnes atteintes de maladies rares, un accompagnement pluridisciplinaire, depuis le diagnostic jusqu’au suivi, impliquant professionnels spécialisés, de proximité, médico-social, social et associations.</t>
+  </si>
+  <si>
     <t>594</t>
   </si>
   <si>
-    <t>Coordination hospitalière de prélèvement de tissus</t>
+    <t>Coordination hospitalière de prélèvement de tissu</t>
   </si>
   <si>
     <t>595</t>
   </si>
   <si>
-    <t>Coordination hospitalière de prélèvement de tissus pédiatrique</t>
+    <t>Coordination hospitalière de prélèvement de tissu pédiatrique</t>
   </si>
   <si>
     <t>596</t>
   </si>
   <si>
-    <t>Coordination hospitalière de prélèvement d’organes pédiatrique</t>
+    <t>Coordination hospitalière de prélèvement d’organe pédiatrique</t>
   </si>
   <si>
     <t>Evaluation de la mémoire (bilan mémoire)</t>
+  </si>
+  <si>
+    <t>Evaluation clinique spécialisée qui mesure de façon formelle les capacités mnésiques  (encodage, stockage, restitution ) et recherche leur retentissement sur la vie quotidienne, à l’aide de tests validés, d’un entretien, et d’examens complémentaires afin de poser un diagnostic ou d’orienter vers une prise en charge adaptée.</t>
   </si>
 </sst>
 </file>
@@ -12251,17 +12257,19 @@
       <c r="C594" t="s" s="2">
         <v>1423</v>
       </c>
-      <c r="D594" s="2"/>
+      <c r="D594" t="s" s="2">
+        <v>1424</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B595" t="s" s="2">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="C595" t="s" s="2">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D595" s="2"/>
     </row>
@@ -12270,10 +12278,10 @@
         <v>58</v>
       </c>
       <c r="B596" t="s" s="2">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C596" t="s" s="2">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="D596" s="2"/>
     </row>
@@ -12282,10 +12290,10 @@
         <v>58</v>
       </c>
       <c r="B597" t="s" s="2">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="C597" t="s" s="2">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="D597" s="2"/>
     </row>
@@ -12297,9 +12305,11 @@
         <v>34</v>
       </c>
       <c r="C598" t="s" s="2">
-        <v>1430</v>
-      </c>
-      <c r="D598" s="2"/>
+        <v>1431</v>
+      </c>
+      <c r="D598" t="s" s="2">
+        <v>1432</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
